--- a/artfynd/A 17442-2025 artfynd.xlsx
+++ b/artfynd/A 17442-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129850996</v>
       </c>
       <c r="B2" t="n">
-        <v>58595</v>
+        <v>58598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129850997</v>
       </c>
       <c r="B3" t="n">
-        <v>58593</v>
+        <v>58596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17442-2025 artfynd.xlsx
+++ b/artfynd/A 17442-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129850996</v>
       </c>
       <c r="B2" t="n">
-        <v>58598</v>
+        <v>58601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129850997</v>
       </c>
       <c r="B3" t="n">
-        <v>58596</v>
+        <v>58599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17442-2025 artfynd.xlsx
+++ b/artfynd/A 17442-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129850996</v>
       </c>
       <c r="B2" t="n">
-        <v>58601</v>
+        <v>58602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129850997</v>
       </c>
       <c r="B3" t="n">
-        <v>58599</v>
+        <v>58600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17442-2025 artfynd.xlsx
+++ b/artfynd/A 17442-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129850996</v>
       </c>
       <c r="B2" t="n">
-        <v>58603</v>
+        <v>58688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129850997</v>
       </c>
       <c r="B3" t="n">
-        <v>58601</v>
+        <v>58686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
